--- a/data/Monster.xlsx
+++ b/data/Monster.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -509,10 +509,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -538,10 +538,10 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>3040</v>
+        <v>1430</v>
       </c>
       <c r="D8" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -553,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I8" t="n">
         <v>30</v>
@@ -567,10 +567,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>4090</v>
+        <v>2010</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -596,10 +596,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>5570</v>
+        <v>2660</v>
       </c>
       <c r="D10" t="n">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
@@ -611,7 +611,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I10" t="n">
         <v>50</v>
@@ -625,10 +625,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>6540</v>
+        <v>3140</v>
       </c>
       <c r="D11" t="n">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>
@@ -640,7 +640,7 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="I11" t="n">
         <v>80</v>
@@ -654,10 +654,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>7670</v>
+        <v>3740</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>92</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -683,10 +683,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>9100</v>
+        <v>4400</v>
       </c>
       <c r="D13" t="n">
-        <v>260</v>
+        <v>106</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -698,7 +698,7 @@
         <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="I13" t="n">
         <v>130</v>
@@ -712,10 +712,10 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>10830</v>
+        <v>5270</v>
       </c>
       <c r="D14" t="n">
-        <v>301</v>
+        <v>121</v>
       </c>
       <c r="E14" t="n">
         <v>14</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="I14" t="n">
         <v>160</v>
@@ -741,10 +741,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>11940</v>
+        <v>5780</v>
       </c>
       <c r="D15" t="n">
-        <v>350</v>
+        <v>135</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
@@ -756,7 +756,7 @@
         <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="I15" t="n">
         <v>200</v>
@@ -770,10 +770,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>14190</v>
+        <v>6890</v>
       </c>
       <c r="D16" t="n">
-        <v>407</v>
+        <v>154</v>
       </c>
       <c r="E16" t="n">
         <v>18</v>
@@ -785,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="I16" t="n">
         <v>260</v>
@@ -799,10 +799,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>14940</v>
+        <v>7230</v>
       </c>
       <c r="D17" t="n">
-        <v>448</v>
+        <v>168</v>
       </c>
       <c r="E17" t="n">
         <v>20</v>
@@ -814,7 +814,7 @@
         <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="I17" t="n">
         <v>320</v>
@@ -828,10 +828,10 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>17520</v>
+        <v>8550</v>
       </c>
       <c r="D18" t="n">
-        <v>529</v>
+        <v>192</v>
       </c>
       <c r="E18" t="n">
         <v>22</v>
@@ -843,7 +843,7 @@
         <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="I18" t="n">
         <v>400</v>
@@ -857,10 +857,10 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>18870</v>
+        <v>9190</v>
       </c>
       <c r="D19" t="n">
-        <v>603</v>
+        <v>216</v>
       </c>
       <c r="E19" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="I19" t="n">
         <v>520</v>
@@ -886,10 +886,10 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>22260</v>
+        <v>10910</v>
       </c>
       <c r="D20" t="n">
-        <v>709</v>
+        <v>249</v>
       </c>
       <c r="E20" t="n">
         <v>28</v>
@@ -901,7 +901,7 @@
         <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="I20" t="n">
         <v>680</v>
@@ -915,10 +915,10 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>50720</v>
+        <v>23850</v>
       </c>
       <c r="D21" t="n">
-        <v>686</v>
+        <v>365</v>
       </c>
       <c r="E21" t="n">
         <v>35</v>
@@ -930,7 +930,7 @@
         <v>25</v>
       </c>
       <c r="H21" t="n">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="I21" t="n">
         <v>1200</v>

--- a/data/Monster.xlsx
+++ b/data/Monster.xlsx
@@ -486,7 +486,7 @@
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
@@ -515,7 +515,7 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -524,7 +524,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="I7" t="n">
         <v>25</v>
@@ -538,13 +538,13 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>1430</v>
+        <v>760</v>
       </c>
       <c r="D8" t="n">
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -553,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>29</v>
+        <v>346</v>
       </c>
       <c r="I8" t="n">
         <v>30</v>
@@ -567,13 +567,13 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="D9" t="n">
         <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>34</v>
+        <v>410</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -596,13 +596,13 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>2660</v>
+        <v>1380</v>
       </c>
       <c r="D10" t="n">
         <v>73</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -611,7 +611,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>475</v>
       </c>
       <c r="I10" t="n">
         <v>50</v>
@@ -625,13 +625,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>3140</v>
+        <v>1620</v>
       </c>
       <c r="D11" t="n">
         <v>82</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -640,7 +640,7 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>45</v>
+        <v>540</v>
       </c>
       <c r="I11" t="n">
         <v>80</v>
@@ -654,13 +654,13 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>3740</v>
+        <v>1920</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>605</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -683,13 +683,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>4400</v>
+        <v>2250</v>
       </c>
       <c r="D13" t="n">
         <v>106</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="F13" t="n">
         <v>15</v>
@@ -698,7 +698,7 @@
         <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>58</v>
+        <v>702</v>
       </c>
       <c r="I13" t="n">
         <v>130</v>
@@ -712,13 +712,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>5270</v>
+        <v>2690</v>
       </c>
       <c r="D14" t="n">
         <v>121</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="F14" t="n">
         <v>15</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>67</v>
+        <v>799</v>
       </c>
       <c r="I14" t="n">
         <v>160</v>
@@ -741,13 +741,13 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>5780</v>
+        <v>2940</v>
       </c>
       <c r="D15" t="n">
         <v>135</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="F15" t="n">
         <v>20</v>
@@ -756,7 +756,7 @@
         <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>75</v>
+        <v>896</v>
       </c>
       <c r="I15" t="n">
         <v>200</v>
@@ -770,13 +770,13 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>6890</v>
+        <v>3500</v>
       </c>
       <c r="D16" t="n">
         <v>154</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>216</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
@@ -785,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>86</v>
+        <v>1026</v>
       </c>
       <c r="I16" t="n">
         <v>260</v>
@@ -799,13 +799,13 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>7230</v>
+        <v>3670</v>
       </c>
       <c r="D17" t="n">
         <v>168</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="F17" t="n">
         <v>25</v>
@@ -814,7 +814,7 @@
         <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>1123</v>
       </c>
       <c r="I17" t="n">
         <v>320</v>
@@ -828,13 +828,13 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>8550</v>
+        <v>4340</v>
       </c>
       <c r="D18" t="n">
         <v>192</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
+        <v>264</v>
       </c>
       <c r="F18" t="n">
         <v>25</v>
@@ -843,7 +843,7 @@
         <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>107</v>
+        <v>1285</v>
       </c>
       <c r="I18" t="n">
         <v>400</v>
@@ -857,13 +857,13 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>9190</v>
+        <v>4670</v>
       </c>
       <c r="D19" t="n">
         <v>216</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="F19" t="n">
         <v>30</v>
@@ -872,7 +872,7 @@
         <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>121</v>
+        <v>1447</v>
       </c>
       <c r="I19" t="n">
         <v>520</v>
@@ -886,13 +886,13 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>10910</v>
+        <v>5550</v>
       </c>
       <c r="D20" t="n">
         <v>249</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="F20" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
         <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>140</v>
+        <v>1674</v>
       </c>
       <c r="I20" t="n">
         <v>680</v>
@@ -915,13 +915,13 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>23850</v>
+        <v>12130</v>
       </c>
       <c r="D21" t="n">
         <v>365</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>420</v>
       </c>
       <c r="F21" t="n">
         <v>40</v>
@@ -930,7 +930,7 @@
         <v>25</v>
       </c>
       <c r="H21" t="n">
-        <v>110</v>
+        <v>1320</v>
       </c>
       <c r="I21" t="n">
         <v>1200</v>

--- a/data/Monster.xlsx
+++ b/data/Monster.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,19 +459,32 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>exp_reward</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>gold_reward</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
           <t>战斗属性与掉落。字段号抄自 generated/code/proto/monster_table.proto,纯追加,1 号未动。</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>击杀掉落:每槽 (物品id, 数量, 万分比概率)</t>
         </is>
       </c>
     </row>
@@ -498,9 +511,18 @@
         <v>240</v>
       </c>
       <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O6" t="n">
         <v>20</v>
       </c>
-      <c r="J6" t="n">
+      <c r="P6" t="n">
         <v>10</v>
       </c>
     </row>
@@ -527,9 +549,27 @@
         <v>252</v>
       </c>
       <c r="I7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O7" t="n">
         <v>25</v>
       </c>
-      <c r="J7" t="n">
+      <c r="P7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -555,10 +595,10 @@
       <c r="H8" t="n">
         <v>346</v>
       </c>
-      <c r="I8" t="n">
+      <c r="O8" t="n">
         <v>30</v>
       </c>
-      <c r="J8" t="n">
+      <c r="P8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -584,10 +624,10 @@
       <c r="H9" t="n">
         <v>410</v>
       </c>
-      <c r="I9" t="n">
+      <c r="O9" t="n">
         <v>40</v>
       </c>
-      <c r="J9" t="n">
+      <c r="P9" t="n">
         <v>20</v>
       </c>
     </row>
@@ -613,10 +653,10 @@
       <c r="H10" t="n">
         <v>475</v>
       </c>
-      <c r="I10" t="n">
+      <c r="O10" t="n">
         <v>50</v>
       </c>
-      <c r="J10" t="n">
+      <c r="P10" t="n">
         <v>25</v>
       </c>
     </row>
@@ -642,10 +682,10 @@
       <c r="H11" t="n">
         <v>540</v>
       </c>
-      <c r="I11" t="n">
+      <c r="O11" t="n">
         <v>80</v>
       </c>
-      <c r="J11" t="n">
+      <c r="P11" t="n">
         <v>40</v>
       </c>
     </row>
@@ -671,10 +711,10 @@
       <c r="H12" t="n">
         <v>605</v>
       </c>
-      <c r="I12" t="n">
+      <c r="O12" t="n">
         <v>100</v>
       </c>
-      <c r="J12" t="n">
+      <c r="P12" t="n">
         <v>55</v>
       </c>
     </row>
@@ -700,10 +740,10 @@
       <c r="H13" t="n">
         <v>702</v>
       </c>
-      <c r="I13" t="n">
+      <c r="O13" t="n">
         <v>130</v>
       </c>
-      <c r="J13" t="n">
+      <c r="P13" t="n">
         <v>70</v>
       </c>
     </row>
@@ -729,10 +769,10 @@
       <c r="H14" t="n">
         <v>799</v>
       </c>
-      <c r="I14" t="n">
+      <c r="O14" t="n">
         <v>160</v>
       </c>
-      <c r="J14" t="n">
+      <c r="P14" t="n">
         <v>90</v>
       </c>
     </row>
@@ -758,10 +798,10 @@
       <c r="H15" t="n">
         <v>896</v>
       </c>
-      <c r="I15" t="n">
+      <c r="O15" t="n">
         <v>200</v>
       </c>
-      <c r="J15" t="n">
+      <c r="P15" t="n">
         <v>120</v>
       </c>
     </row>
@@ -787,10 +827,10 @@
       <c r="H16" t="n">
         <v>1026</v>
       </c>
-      <c r="I16" t="n">
+      <c r="O16" t="n">
         <v>260</v>
       </c>
-      <c r="J16" t="n">
+      <c r="P16" t="n">
         <v>150</v>
       </c>
     </row>
@@ -816,10 +856,10 @@
       <c r="H17" t="n">
         <v>1123</v>
       </c>
-      <c r="I17" t="n">
+      <c r="O17" t="n">
         <v>320</v>
       </c>
-      <c r="J17" t="n">
+      <c r="P17" t="n">
         <v>190</v>
       </c>
     </row>
@@ -845,10 +885,10 @@
       <c r="H18" t="n">
         <v>1285</v>
       </c>
-      <c r="I18" t="n">
+      <c r="O18" t="n">
         <v>400</v>
       </c>
-      <c r="J18" t="n">
+      <c r="P18" t="n">
         <v>240</v>
       </c>
     </row>
@@ -874,10 +914,10 @@
       <c r="H19" t="n">
         <v>1447</v>
       </c>
-      <c r="I19" t="n">
+      <c r="O19" t="n">
         <v>520</v>
       </c>
-      <c r="J19" t="n">
+      <c r="P19" t="n">
         <v>300</v>
       </c>
     </row>
@@ -903,10 +943,10 @@
       <c r="H20" t="n">
         <v>1674</v>
       </c>
-      <c r="I20" t="n">
+      <c r="O20" t="n">
         <v>680</v>
       </c>
-      <c r="J20" t="n">
+      <c r="P20" t="n">
         <v>400</v>
       </c>
     </row>
@@ -932,10 +972,10 @@
       <c r="H21" t="n">
         <v>1320</v>
       </c>
-      <c r="I21" t="n">
+      <c r="O21" t="n">
         <v>1200</v>
       </c>
-      <c r="J21" t="n">
+      <c r="P21" t="n">
         <v>800</v>
       </c>
     </row>

--- a/data/Monster.xlsx
+++ b/data/Monster.xlsx
@@ -495,8 +495,8 @@
       <c r="C6" t="n">
         <v>370</v>
       </c>
-      <c r="D6" t="n">
-        <v>14</v>
+      <c r="D6">
+        <v>30</v>
       </c>
       <c r="E6" t="n">
         <v>36</v>
@@ -533,8 +533,8 @@
       <c r="C7" t="n">
         <v>360</v>
       </c>
-      <c r="D7" t="n">
-        <v>14</v>
+      <c r="D7">
+        <v>32</v>
       </c>
       <c r="E7" t="n">
         <v>48</v>
@@ -577,11 +577,11 @@
       <c r="A8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>760</v>
-      </c>
-      <c r="D8" t="n">
-        <v>53</v>
+      <c r="C8">
+        <v>900</v>
+      </c>
+      <c r="D8">
+        <v>65</v>
       </c>
       <c r="E8" t="n">
         <v>60</v>
@@ -606,11 +606,11 @@
       <c r="A9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D9" t="n">
-        <v>63</v>
+      <c r="C9">
+        <v>1250</v>
+      </c>
+      <c r="D9">
+        <v>90</v>
       </c>
       <c r="E9" t="n">
         <v>72</v>
@@ -635,11 +635,11 @@
       <c r="A10" t="n">
         <v>5</v>
       </c>
-      <c r="C10" t="n">
-        <v>1380</v>
-      </c>
-      <c r="D10" t="n">
-        <v>73</v>
+      <c r="C10">
+        <v>1650</v>
+      </c>
+      <c r="D10">
+        <v>115</v>
       </c>
       <c r="E10" t="n">
         <v>84</v>
@@ -664,11 +664,11 @@
       <c r="A11" t="n">
         <v>6</v>
       </c>
-      <c r="C11" t="n">
-        <v>1620</v>
-      </c>
-      <c r="D11" t="n">
-        <v>82</v>
+      <c r="C11">
+        <v>2000</v>
+      </c>
+      <c r="D11">
+        <v>140</v>
       </c>
       <c r="E11" t="n">
         <v>96</v>
@@ -693,11 +693,11 @@
       <c r="A12" t="n">
         <v>7</v>
       </c>
-      <c r="C12" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D12" t="n">
-        <v>92</v>
+      <c r="C12">
+        <v>2400</v>
+      </c>
+      <c r="D12">
+        <v>165</v>
       </c>
       <c r="E12" t="n">
         <v>120</v>
@@ -722,11 +722,11 @@
       <c r="A13" t="n">
         <v>8</v>
       </c>
-      <c r="C13" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D13" t="n">
-        <v>106</v>
+      <c r="C13">
+        <v>2850</v>
+      </c>
+      <c r="D13">
+        <v>200</v>
       </c>
       <c r="E13" t="n">
         <v>144</v>
@@ -751,11 +751,11 @@
       <c r="A14" t="n">
         <v>9</v>
       </c>
-      <c r="C14" t="n">
-        <v>2690</v>
-      </c>
-      <c r="D14" t="n">
-        <v>121</v>
+      <c r="C14">
+        <v>3400</v>
+      </c>
+      <c r="D14">
+        <v>235</v>
       </c>
       <c r="E14" t="n">
         <v>168</v>
@@ -780,11 +780,11 @@
       <c r="A15" t="n">
         <v>10</v>
       </c>
-      <c r="C15" t="n">
-        <v>2940</v>
-      </c>
-      <c r="D15" t="n">
-        <v>135</v>
+      <c r="C15">
+        <v>4000</v>
+      </c>
+      <c r="D15">
+        <v>280</v>
       </c>
       <c r="E15" t="n">
         <v>192</v>
@@ -809,11 +809,11 @@
       <c r="A16" t="n">
         <v>11</v>
       </c>
-      <c r="C16" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D16" t="n">
-        <v>154</v>
+      <c r="C16">
+        <v>4600</v>
+      </c>
+      <c r="D16">
+        <v>190</v>
       </c>
       <c r="E16" t="n">
         <v>216</v>
@@ -838,11 +838,11 @@
       <c r="A17" t="n">
         <v>12</v>
       </c>
-      <c r="C17" t="n">
-        <v>3670</v>
-      </c>
-      <c r="D17" t="n">
-        <v>168</v>
+      <c r="C17">
+        <v>5000</v>
+      </c>
+      <c r="D17">
+        <v>210</v>
       </c>
       <c r="E17" t="n">
         <v>240</v>
@@ -867,11 +867,11 @@
       <c r="A18" t="n">
         <v>13</v>
       </c>
-      <c r="C18" t="n">
-        <v>4340</v>
-      </c>
-      <c r="D18" t="n">
-        <v>192</v>
+      <c r="C18">
+        <v>6000</v>
+      </c>
+      <c r="D18">
+        <v>420</v>
       </c>
       <c r="E18" t="n">
         <v>264</v>
@@ -896,11 +896,11 @@
       <c r="A19" t="n">
         <v>14</v>
       </c>
-      <c r="C19" t="n">
-        <v>4670</v>
-      </c>
-      <c r="D19" t="n">
-        <v>216</v>
+      <c r="C19">
+        <v>7000</v>
+      </c>
+      <c r="D19">
+        <v>500</v>
       </c>
       <c r="E19" t="n">
         <v>300</v>
@@ -925,11 +925,11 @@
       <c r="A20" t="n">
         <v>15</v>
       </c>
-      <c r="C20" t="n">
-        <v>5550</v>
-      </c>
-      <c r="D20" t="n">
-        <v>249</v>
+      <c r="C20">
+        <v>8500</v>
+      </c>
+      <c r="D20">
+        <v>600</v>
       </c>
       <c r="E20" t="n">
         <v>336</v>
@@ -954,11 +954,11 @@
       <c r="A21" t="n">
         <v>16</v>
       </c>
-      <c r="C21" t="n">
-        <v>12130</v>
-      </c>
-      <c r="D21" t="n">
-        <v>365</v>
+      <c r="C21">
+        <v>10500</v>
+      </c>
+      <c r="D21">
+        <v>320</v>
       </c>
       <c r="E21" t="n">
         <v>420</v>
